--- a/output/pdf_financials_xlsx/MCB.xlsx
+++ b/output/pdf_financials_xlsx/MCB.xlsx
@@ -4625,10 +4625,10 @@
         <v>7.591815</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>15.504</v>
+        <v>0.632</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>3.814</v>
+        <v>3.856</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>0</v>
@@ -40742,7 +40742,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">

--- a/output/pdf_financials_xlsx/MCB.xlsx
+++ b/output/pdf_financials_xlsx/MCB.xlsx
@@ -1496,10 +1496,10 @@
         <v>1.039</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>2.755</v>
+        <v>52.917</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>3.003</v>
+        <v>50.515</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>3.384</v>
@@ -1556,10 +1556,10 @@
         <v>-6.748</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.229</v>
+        <v>-49.933</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>9.683</v>
+        <v>-37.829</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>12.944</v>
@@ -3505,15 +3505,11 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>4.449866</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>4.871</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>3.782</v>
@@ -3659,15 +3655,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>4.449866</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>4.871</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>3.782</v>
@@ -4622,13 +4614,13 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>7.591815</v>
+        <v>3.141949</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0.632</v>
+        <v>10.633</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>3.856</v>
+        <v>3.814</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>0</v>
@@ -10252,22 +10244,22 @@
         <v>0</v>
       </c>
       <c r="M139" s="3" t="n">
-        <v>0</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="N139" s="3" t="n">
-        <v>0</v>
+        <v>-0.782</v>
       </c>
       <c r="O139" s="3" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="P139" s="3" t="n">
-        <v>0</v>
+        <v>-1.124</v>
       </c>
       <c r="Q139" s="3" t="n">
-        <v>0</v>
+        <v>-2.33</v>
       </c>
       <c r="R139" s="3" t="n">
-        <v>0</v>
+        <v>-3.394</v>
       </c>
     </row>
     <row r="140">
@@ -10310,22 +10302,22 @@
         <v>0</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>0</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>0</v>
+        <v>-0.782</v>
       </c>
       <c r="O140" s="3" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="P140" s="3" t="n">
-        <v>0</v>
+        <v>-1.124</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>0</v>
+        <v>-2.33</v>
       </c>
       <c r="R140" s="3" t="n">
-        <v>0</v>
+        <v>-3.394</v>
       </c>
     </row>
     <row r="141">
@@ -40330,7 +40322,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -40742,7 +40734,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -43053,7 +43045,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E322" s="5" t="n">
@@ -48592,7 +48584,11 @@
           <t>Principal elements of lease payments 12</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -49583,7 +49579,11 @@
           <t>Principal elements of lease payments</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -57465,7 +57465,11 @@
           <t>Principal elements of lease payments</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -82250,7 +82254,7 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -82765,7 +82769,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">

--- a/output/pdf_financials_xlsx/MCB.xlsx
+++ b/output/pdf_financials_xlsx/MCB.xlsx
@@ -2696,22 +2696,22 @@
         <v>1.153</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.189</v>
+        <v>4.351</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1.008</v>
+        <v>3.343</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1.163</v>
+        <v>4.256</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>2.681</v>
+        <v>6.36</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>3.173</v>
+        <v>7.611</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.226</v>
+        <v>4.691</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>3.154</v>
@@ -2720,22 +2720,22 @@
         <v>3.158</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0.155</v>
+        <v>2.884</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0.792</v>
+        <v>2.959</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>1.151</v>
+        <v>2.997</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>1.823</v>
+        <v>3.808</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>1.922</v>
+        <v>4.304</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>1.902</v>
+        <v>5.063</v>
       </c>
     </row>
     <row r="35">
@@ -2754,22 +2754,22 @@
         <v>9.9762</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>17.44345</v>
+        <v>20.60545</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>26.493</v>
+        <v>28.828</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>22.091</v>
+        <v>25.184</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>33.855</v>
+        <v>37.534</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>-7.865</v>
+        <v>-3.427</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>-38.435</v>
+        <v>-34.97</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>-14.132</v>
@@ -2778,22 +2778,22 @@
         <v>-0.314</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>0.388</v>
+        <v>3.117</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>4.87</v>
+        <v>7.037</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>8.94</v>
+        <v>10.786</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>8.91</v>
+        <v>10.895</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>11.822</v>
+        <v>14.204</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>11.519</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="36">
@@ -2814,22 +2814,22 @@
         <v>9.900166719593521</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>11.34186622625929</v>
+        <v>13.39782310448188</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>26.01254823411588</v>
+        <v>28.30520290239281</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>20.04409683156099</v>
+        <v>22.85050629695496</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>28.06771735796185</v>
+        <v>31.11781725930409</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-9.617736255135981</v>
+        <v>-4.190716102523968</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-142.3571243379384</v>
+        <v>-129.5233156783585</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>-35.29029841428393</v>
@@ -2838,22 +2838,22 @@
         <v>-0.6398239465319097</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.7267006293077615</v>
+        <v>5.837953251423434</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>14.84937187461886</v>
+        <v>21.4568849859739</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>17.05195696955825</v>
+        <v>20.57297627222095</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>12.78537502331788</v>
+        <v>15.63374420640273</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>15.25104494555963</v>
+        <v>18.32395892460911</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>13.74926890987002</v>
+        <v>17.52229078886117</v>
       </c>
     </row>
     <row r="37">
@@ -8815,49 +8815,49 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1.153</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>4.351</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>3.343</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>4.256</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>7.611</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>4.691</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>3.154</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>3.158</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>2.884</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>2.959</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>2.997</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>3.808</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>4.304</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>5.063</v>
       </c>
     </row>
     <row r="116">
@@ -9508,10 +9508,10 @@
         <v>0</v>
       </c>
       <c r="C127" s="3" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E127" s="3" t="n">
         <v>0</v>
@@ -46841,7 +46841,11 @@
           <t>Depreciation of property, plant and equipment 6</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -46928,7 +46932,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -47921,7 +47925,11 @@
           <t>Additions to intangible assets 7</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -57079,7 +57087,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>-</t>
@@ -59633,7 +59645,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -59732,7 +59748,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -62454,7 +62470,11 @@
           <t>Depreciation of property, plant and equipment 17</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E521" t="inlineStr">
         <is>
           <t>-</t>
@@ -62555,7 +62575,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -64121,7 +64141,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
           <t>-</t>
@@ -64220,7 +64244,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -69178,7 +69202,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E589" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MCB.xlsx
+++ b/output/pdf_financials_xlsx/MCB.xlsx
@@ -2151,10 +2151,8 @@
       <c r="L26" s="3" t="n">
         <v>-3.791</v>
       </c>
-      <c r="M26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M26" s="3" t="n">
+        <v>0.233</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>4.078</v>
@@ -6110,75 +6108,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E79" s="3" t="n">
+        <v>10.206</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>9.153</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>7.219</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>6.552</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>2.911</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>1.731</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>3.211</v>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>5.409</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>3.26</v>
       </c>
     </row>
     <row r="80">
@@ -6197,46 +6167,46 @@
         <v>15.765</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>14.61</v>
+        <v>24.816</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>19.419</v>
+        <v>28.572</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>15.293</v>
+        <v>22.512</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>15.119</v>
+        <v>21.671</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>6.532</v>
+        <v>9.443</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>3.655</v>
+        <v>4.766</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>5.563</v>
+        <v>7.044</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>9.726000000000001</v>
+        <v>11.372</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>5.584</v>
+        <v>6.764</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>4.897</v>
+        <v>5.942</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>10.862</v>
+        <v>12.593</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>13.35</v>
+        <v>16.561</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>19.735</v>
+        <v>25.144</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>16.189</v>
+        <v>19.449</v>
       </c>
     </row>
     <row r="81">
@@ -6341,20 +6311,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D82" s="3" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0.253</v>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
@@ -6386,35 +6350,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M82" s="3" t="n">
+        <v>2.164</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>3.051</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>4.428</v>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="Q82" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>1.407</v>
       </c>
     </row>
     <row r="83">
@@ -6430,17 +6382,13 @@
         <v>0.844</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.858</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0.253</v>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
@@ -6472,35 +6420,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M83" s="3" t="n">
+        <v>2.164</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>3.051</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>4.428</v>
+      </c>
+      <c r="P83" s="3" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="Q83" s="3" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>1.407</v>
       </c>
     </row>
     <row r="84">
@@ -6796,47 +6732,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E87" s="3" t="n">
-        <v>2.882</v>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F87" s="3" t="n">
         <v>0.133</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>9.369999999999999</v>
+        <v>2.151</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>10.368</v>
+        <v>3.816</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>6.112</v>
+        <v>3.201</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>2.805</v>
+        <v>1.694</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>10.003</v>
+        <v>8.522</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>5.654</v>
+        <v>4.008</v>
       </c>
       <c r="M87" s="3" t="n">
-        <v>8.317</v>
-      </c>
-      <c r="N87" s="3" t="n">
-        <v>3.49</v>
+        <v>4.973</v>
+      </c>
+      <c r="N87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O87" s="3" t="n">
-        <v>8.537000000000001</v>
+        <v>2.378</v>
       </c>
       <c r="P87" s="3" t="n">
-        <v>6.7</v>
+        <v>0.281</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>9.401999999999999</v>
+        <v>1.476</v>
       </c>
       <c r="R87" s="3" t="n">
-        <v>5.887</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="88">
@@ -7174,17 +7114,13 @@
         <v>0.109980527662174</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.1005770517899459</v>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1079213472983484</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.006011791081956324</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.003264684628884071</v>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
@@ -7216,35 +7152,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M92" s="3" t="n">
+        <v>0.05717305151915456</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>0.07625593601599601</v>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>0.08562478245736165</v>
+      </c>
+      <c r="P92" s="3" t="n">
+        <v>0.05942611562899431</v>
+      </c>
+      <c r="Q92" s="3" t="n">
+        <v>0.03802401994108316</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>0.02050751359151132</v>
       </c>
     </row>
     <row r="93">
@@ -9224,46 +9148,46 @@
         <v>0.364</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>0</v>
+        <v>0.485</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>0</v>
+        <v>0.711</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>0</v>
+        <v>0.695</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>0</v>
+        <v>0.208</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>0</v>
+        <v>0.393</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>0</v>
+        <v>0.332</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>0</v>
+        <v>0.218</v>
       </c>
       <c r="L122" s="3" t="n">
-        <v>0</v>
+        <v>0.203</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>0</v>
+        <v>0.592</v>
       </c>
       <c r="O122" s="3" t="n">
-        <v>0</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="P122" s="3" t="n">
-        <v>0</v>
+        <v>1.307</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R122" s="3" t="n">
-        <v>0</v>
+        <v>0.783</v>
       </c>
     </row>
     <row r="123">
@@ -9294,16 +9218,16 @@
         <v>0</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0</v>
+        <v>5.898</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0</v>
+        <v>6.645</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>0</v>
+        <v>0.606</v>
       </c>
       <c r="L123" s="3" t="n">
-        <v>0</v>
+        <v>0.902</v>
       </c>
       <c r="M123" s="3" t="n">
         <v>0</v>
@@ -9743,10 +9667,10 @@
         <v>0</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>0</v>
+        <v>-0.733</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="F131" s="3" t="n">
         <v>0</v>
@@ -9933,10 +9857,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I134" s="3" t="n">
+        <v>-3.396</v>
       </c>
       <c r="J134" s="1" t="inlineStr">
         <is>
@@ -10064,19 +9986,19 @@
         <v>0</v>
       </c>
       <c r="K136" s="3" t="n">
-        <v>0</v>
+        <v>-0.061</v>
       </c>
       <c r="L136" s="3" t="n">
-        <v>0</v>
+        <v>-0.265</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>0</v>
+        <v>-0.068</v>
       </c>
       <c r="N136" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O136" s="3" t="n">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
       <c r="P136" s="3" t="n">
         <v>0</v>
@@ -10549,10 +10471,8 @@
       <c r="F144" s="3" t="n">
         <v>-1.716</v>
       </c>
-      <c r="G144" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G144" s="3" t="n">
+        <v>-13.257</v>
       </c>
       <c r="H144" s="1" t="inlineStr">
         <is>
@@ -10573,10 +10493,8 @@
       <c r="L144" s="3" t="n">
         <v>1.941</v>
       </c>
-      <c r="M144" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M144" s="3" t="n">
+        <v>-0.42</v>
       </c>
       <c r="N144" s="1" t="inlineStr">
         <is>
@@ -10901,28 +10819,22 @@
         <v>7.667</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>13.01</v>
+        <v>13.282</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>14.257</v>
+        <v>13.755</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>-2.513</v>
-      </c>
-      <c r="G150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.047</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>3.253</v>
+      </c>
+      <c r="I150" s="3" t="n">
+        <v>2.189</v>
       </c>
       <c r="J150" s="3" t="n">
         <v>-8.061999999999999</v>
@@ -10933,29 +10845,23 @@
       <c r="L150" s="3" t="n">
         <v>-5.999</v>
       </c>
-      <c r="M150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M150" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N150" s="3" t="n">
+        <v>-0.446</v>
+      </c>
+      <c r="O150" s="3" t="n">
+        <v>1.755</v>
       </c>
       <c r="P150" s="3" t="n">
-        <v>1.958</v>
+        <v>2.291</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>5.492</v>
+        <v>4.544</v>
       </c>
       <c r="R150" s="3" t="n">
-        <v>-6.188</v>
+        <v>-5.962</v>
       </c>
     </row>
   </sheetData>
@@ -12875,7 +12781,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -36210,7 +36120,11 @@
           <t>Current portion of finance lease obligations 133</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -39197,7 +39111,11 @@
           <t>Current portion of finance lease obligations 12 253</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -47213,7 +47131,11 @@
           <t>Share-based compensation expense 15</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
@@ -47660,7 +47582,11 @@
           <t>Net cash (used in) generated from operating activities</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -51749,7 +51675,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -53374,7 +53304,11 @@
           <t>Repurchase of shares 14</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
@@ -56703,7 +56637,11 @@
           <t>Impairment charges 7</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -56901,7 +56839,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr">
         <is>
           <t>-</t>
@@ -57277,7 +57219,11 @@
           <t>Repurchase of common shares 14</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E468" t="inlineStr">
         <is>
           <t>-</t>
@@ -58265,7 +58211,11 @@
           <t>Share-based compensation expense 14</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>
@@ -58362,7 +58312,11 @@
           <t>Impairment charges 6, 7</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -58855,7 +58809,11 @@
           <t>Repurchase of shares 13b</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -59344,7 +59302,11 @@
           <t>Repurchase of shares 25</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr">
         <is>
           <t>-</t>
@@ -59948,7 +59910,11 @@
           <t>Impairment charges 7, 8</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
           <t>-</t>
@@ -61118,7 +61084,11 @@
           <t>Share-based compensation expense 15(c)</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -64341,7 +64311,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
           <t>-</t>
@@ -64440,7 +64414,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>-</t>
@@ -65319,7 +65297,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
           <t>-</t>
@@ -65612,7 +65594,11 @@
           <t>Share based compensation expense 14</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
           <t>-</t>
@@ -66511,7 +66497,11 @@
           <t>Share based compensation expense 15</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr"/>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E562" t="inlineStr">
         <is>
           <t>-</t>
@@ -67010,7 +67000,11 @@
           <t>Purchases of intangible assets</t>
         </is>
       </c>
-      <c r="D567" t="inlineStr"/>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E567" t="inlineStr">
         <is>
           <t>-</t>
@@ -68307,7 +68301,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E580" s="5" t="n">
         <v>-1.121286</v>
       </c>
@@ -79597,7 +79595,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D694" t="inlineStr"/>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E694" t="inlineStr">
         <is>
           <t>-</t>
@@ -79795,7 +79797,11 @@
           <t>Basic from net earnings (loss)</t>
         </is>
       </c>
-      <c r="D696" t="inlineStr"/>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E696" t="inlineStr">
         <is>
           <t>-</t>
@@ -79894,7 +79900,11 @@
           <t>Diluted from net earnings (loss)</t>
         </is>
       </c>
-      <c r="D697" t="inlineStr"/>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E697" t="inlineStr">
         <is>
           <t>-</t>
@@ -83001,7 +83011,11 @@
           <t>Computed income tax recovery</t>
         </is>
       </c>
-      <c r="D728" t="inlineStr"/>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E728" t="inlineStr">
         <is>
           <t>-</t>
